--- a/Emisiones/4.0 HV-LISTADOS/P2437-HV-LIS-001.xlsx
+++ b/Emisiones/4.0 HV-LISTADOS/P2437-HV-LIS-001.xlsx
@@ -3720,7 +3720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.6" customWidth="1" min="1" max="1"/>
@@ -3743,20 +3743,20 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
@@ -3767,13 +3767,13 @@
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
     <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
-    <col width="13" customWidth="1" min="54" max="54"/>
-    <col width="13" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
@@ -3786,6 +3786,14 @@
     <col width="13" customWidth="1" min="65" max="65"/>
     <col width="13" customWidth="1" min="66" max="66"/>
     <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="13" customWidth="1" min="69" max="69"/>
+    <col width="13" customWidth="1" min="70" max="70"/>
+    <col width="13" customWidth="1" min="71" max="71"/>
+    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="13" customWidth="1" min="73" max="73"/>
+    <col width="13" customWidth="1" min="74" max="74"/>
+    <col width="13" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4055,478 +4063,176 @@
     </row>
     <row r="16" ht="15" customHeight="1"/>
     <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="150" customHeight="1">
+    <row r="18" ht="165" customHeight="1">
       <c r="A18" s="83" t="inlineStr">
         <is>
-          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
+          <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png): ventilador axial mural Ø560 mm de transmisión directa, banco de filtración alojado en la cubierta intemperie, estructura de unión pernada al muro y malla de protección interior. Se eliminan la conexión flexible y la caja/housing con transición cuadrado/circular (REV1).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1"/>
     <row r="20" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="75" customHeight="1">
-      <c r="A22" s="84" t="inlineStr">
-        <is>
-          <t>1. Alcance del suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="83" t="inlineStr">
-        <is>
-          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
-        </is>
-      </c>
-    </row>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="15" customHeight="1"/>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="83" t="inlineStr">
+        <is>
+          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="15" customHeight="1"/>
     <row r="27" ht="15" customHeight="1"/>
     <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="84" t="inlineStr">
+    <row r="29" ht="75" customHeight="1">
+      <c r="A29" s="84" t="inlineStr">
+        <is>
+          <t>1. Alcance del suministro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="83" t="inlineStr">
+        <is>
+          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1"/>
+    <row r="32" ht="15" customHeight="1"/>
+    <row r="33" ht="15" customHeight="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="84" t="inlineStr">
         <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="135" customHeight="1">
-      <c r="A31" s="85" t="inlineStr">
+    <row r="38" ht="135" customHeight="1">
+      <c r="A38" s="85" t="inlineStr">
         <is>
           <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="120" customHeight="1">
-      <c r="A33" s="86" t="inlineStr">
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="86" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B33" s="86" t="inlineStr">
+      <c r="B40" s="86" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C33" s="86" t="n"/>
-      <c r="D33" s="86" t="inlineStr">
+      <c r="C40" s="86" t="n"/>
+      <c r="D40" s="86" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E33" s="86" t="n"/>
-      <c r="F33" s="86" t="n"/>
-      <c r="G33" s="86" t="inlineStr">
+      <c r="E40" s="86" t="n"/>
+      <c r="F40" s="86" t="n"/>
+      <c r="G40" s="86" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H33" s="86" t="n"/>
-      <c r="I33" s="86" t="inlineStr">
+      <c r="H40" s="86" t="n"/>
+      <c r="I40" s="86" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J33" s="86" t="inlineStr">
+      <c r="J40" s="86" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K33" s="86" t="n"/>
-      <c r="L33" s="86" t="n"/>
-      <c r="M33" s="86" t="inlineStr">
+      <c r="K40" s="86" t="n"/>
+      <c r="L40" s="86" t="n"/>
+      <c r="M40" s="86" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N33" s="86" t="n"/>
-      <c r="O33" s="86" t="n"/>
-    </row>
-    <row r="34" ht="810" customHeight="1">
-      <c r="A34" s="87" t="inlineStr">
+      <c r="N40" s="86" t="n"/>
+      <c r="O40" s="86" t="n"/>
+    </row>
+    <row r="41" ht="510" customHeight="1">
+      <c r="A41" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B34" s="87" t="inlineStr">
-        <is>
-          <t>Ventilador de impulsión</t>
-        </is>
-      </c>
-      <c r="C34" s="88" t="n"/>
-      <c r="D34" s="87" t="inlineStr">
-        <is>
-          <t>Axial tubeaxial, transmisión por bandas; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; tamaño/RPM por confirmar con proveedor</t>
-        </is>
-      </c>
-      <c r="E34" s="88" t="n"/>
-      <c r="F34" s="88" t="n"/>
-      <c r="G34" s="87" t="inlineStr">
-        <is>
-          <t>PRFV viniléster (ASTM C582/D4167); motor fuera de la corriente de aire</t>
-        </is>
-      </c>
-      <c r="H34" s="88" t="n"/>
-      <c r="I34" s="87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" s="87" t="inlineStr">
-        <is>
-          <t>Aerovent FBD (Twin City Fan, Catálogo 185); Greenheck VAB (vaneaxial epóxico, Prime Lines HVAC, Bogotá); Sodeca HCT/HGT anticorrosivo PRFV; NYB FRP tubeaxial; Plastec PP</t>
-        </is>
-      </c>
-      <c r="K34" s="88" t="n"/>
-      <c r="L34" s="88" t="n"/>
-      <c r="M34" s="87" t="inlineStr">
-        <is>
-          <t>Aerovent Cat. 185 (PDF) (https://www.aerovent.com/wp-content/uploads/sites/2/2024/07/Fiberglass-Fans-Axial-Flow-Model-FBD-FDP-FRV-TFBD-VTFBD-Catalog-185.pdf); Greenheck VAB/VAD (PDF) (https://content.greenheck.com/public/DAMProd/Original/10003/vane_axial_catalog.pdf); Sodeca (https://www.sodeca.com)</t>
-        </is>
-      </c>
-      <c r="N34" s="88" t="n"/>
-      <c r="O34" s="88" t="n"/>
-    </row>
-    <row r="35" ht="525" customHeight="1">
-      <c r="A35" s="87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B35" s="87" t="inlineStr">
-        <is>
-          <t>Motor del ventilador</t>
-        </is>
-      </c>
-      <c r="C35" s="88" t="n"/>
-      <c r="D35" s="87" t="inlineStr">
-        <is>
-          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="E35" s="88" t="n"/>
-      <c r="F35" s="88" t="n"/>
-      <c r="G35" s="87" t="inlineStr">
-        <is>
-          <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente (transmisión por bandas)</t>
-        </is>
-      </c>
-      <c r="H35" s="88" t="n"/>
-      <c r="I35" s="87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" s="87" t="inlineStr">
-        <is>
-          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
-        </is>
-      </c>
-      <c r="K35" s="88" t="n"/>
-      <c r="L35" s="88" t="n"/>
-      <c r="M35" s="87" t="inlineStr">
-        <is>
-          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
-        </is>
-      </c>
-      <c r="N35" s="88" t="n"/>
-      <c r="O35" s="88" t="n"/>
-    </row>
-    <row r="36" ht="465" customHeight="1">
-      <c r="A36" s="87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B36" s="87" t="inlineStr">
-        <is>
-          <t>Prefiltro (etapa 1)</t>
-        </is>
-      </c>
-      <c r="C36" s="88" t="n"/>
-      <c r="D36" s="87" t="inlineStr">
-        <is>
-          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
-        </is>
-      </c>
-      <c r="E36" s="88" t="n"/>
-      <c r="F36" s="88" t="n"/>
-      <c r="G36" s="87" t="inlineStr">
-        <is>
-          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
-        </is>
-      </c>
-      <c r="H36" s="88" t="n"/>
-      <c r="I36" s="87" t="inlineStr">
-        <is>
-          <t>1 (+ repuestos)</t>
-        </is>
-      </c>
-      <c r="J36" s="87" t="inlineStr">
-        <is>
-          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
-        </is>
-      </c>
-      <c r="K36" s="88" t="n"/>
-      <c r="L36" s="88" t="n"/>
-      <c r="M36" s="87" t="inlineStr">
-        <is>
-          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
-        </is>
-      </c>
-      <c r="N36" s="88" t="n"/>
-      <c r="O36" s="88" t="n"/>
-    </row>
-    <row r="37" ht="660" customHeight="1">
-      <c r="A37" s="87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B37" s="87" t="inlineStr">
-        <is>
-          <t>Filtro final (etapa 2)</t>
-        </is>
-      </c>
-      <c r="C37" s="88" t="n"/>
-      <c r="D37" s="87" t="inlineStr">
-        <is>
-          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
-        </is>
-      </c>
-      <c r="E37" s="88" t="n"/>
-      <c r="F37" s="88" t="n"/>
-      <c r="G37" s="87" t="inlineStr">
-        <is>
-          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
-        </is>
-      </c>
-      <c r="H37" s="88" t="n"/>
-      <c r="I37" s="87" t="inlineStr">
-        <is>
-          <t>1 (+ repuestos)</t>
-        </is>
-      </c>
-      <c r="J37" s="87" t="inlineStr">
-        <is>
-          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
-        </is>
-      </c>
-      <c r="K37" s="88" t="n"/>
-      <c r="L37" s="88" t="n"/>
-      <c r="M37" s="87" t="inlineStr">
-        <is>
-          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
-        </is>
-      </c>
-      <c r="N37" s="88" t="n"/>
-      <c r="O37" s="88" t="n"/>
-    </row>
-    <row r="38" ht="420" customHeight="1">
-      <c r="A38" s="87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B38" s="87" t="inlineStr">
-        <is>
-          <t>Marcos portafiltros</t>
-        </is>
-      </c>
-      <c r="C38" s="88" t="n"/>
-      <c r="D38" s="87" t="inlineStr">
-        <is>
-          <t>Holding frames para prefiltro + filtro final con junta continua</t>
-        </is>
-      </c>
-      <c r="E38" s="88" t="n"/>
-      <c r="F38" s="88" t="n"/>
-      <c r="G38" s="87" t="inlineStr">
-        <is>
-          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
-        </is>
-      </c>
-      <c r="H38" s="88" t="n"/>
-      <c r="I38" s="87" t="inlineStr">
-        <is>
-          <t>1 juego</t>
-        </is>
-      </c>
-      <c r="J38" s="87" t="inlineStr">
-        <is>
-          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
-        </is>
-      </c>
-      <c r="K38" s="88" t="n"/>
-      <c r="L38" s="88" t="n"/>
-      <c r="M38" s="87" t="inlineStr">
-        <is>
-          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
-        </is>
-      </c>
-      <c r="N38" s="88" t="n"/>
-      <c r="O38" s="88" t="n"/>
-    </row>
-    <row r="39" ht="450" customHeight="1">
-      <c r="A39" s="87" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B39" s="87" t="inlineStr">
-        <is>
-          <t>Rejillas de descarga</t>
-        </is>
-      </c>
-      <c r="C39" s="88" t="n"/>
-      <c r="D39" s="87" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
-        </is>
-      </c>
-      <c r="E39" s="88" t="n"/>
-      <c r="F39" s="88" t="n"/>
-      <c r="G39" s="87" t="inlineStr">
-        <is>
-          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
-        </is>
-      </c>
-      <c r="H39" s="88" t="n"/>
-      <c r="I39" s="87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" s="87" t="inlineStr">
-        <is>
-          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
-        </is>
-      </c>
-      <c r="K39" s="88" t="n"/>
-      <c r="L39" s="88" t="n"/>
-      <c r="M39" s="87" t="inlineStr">
-        <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
-        </is>
-      </c>
-      <c r="N39" s="88" t="n"/>
-      <c r="O39" s="88" t="n"/>
-    </row>
-    <row r="40" ht="375" customHeight="1">
-      <c r="A40" s="87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B40" s="87" t="inlineStr">
-        <is>
-          <t>Malla anti-insectos</t>
-        </is>
-      </c>
-      <c r="C40" s="88" t="n"/>
-      <c r="D40" s="87" t="inlineStr">
-        <is>
-          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
-        </is>
-      </c>
-      <c r="E40" s="88" t="n"/>
-      <c r="F40" s="88" t="n"/>
-      <c r="G40" s="87" t="inlineStr">
-        <is>
-          <t>Inox 316</t>
-        </is>
-      </c>
-      <c r="H40" s="88" t="n"/>
-      <c r="I40" s="87" t="inlineStr">
-        <is>
-          <t>3 (una por rejilla)</t>
-        </is>
-      </c>
-      <c r="J40" s="87" t="inlineStr">
-        <is>
-          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
-        </is>
-      </c>
-      <c r="K40" s="88" t="n"/>
-      <c r="L40" s="88" t="n"/>
-      <c r="M40" s="87" t="inlineStr">
-        <is>
-          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
-        </is>
-      </c>
-      <c r="N40" s="88" t="n"/>
-      <c r="O40" s="88" t="n"/>
-    </row>
-    <row r="41" ht="270" customHeight="1">
-      <c r="A41" s="87" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="B41" s="87" t="inlineStr">
         <is>
-          <t>Soportes y ferretería</t>
+          <t>Ventilador de inyección</t>
         </is>
       </c>
       <c r="C41" s="88" t="n"/>
       <c r="D41" s="87" t="inlineStr">
         <is>
-          <t>Soportes de ventilador y rejillas; pernos, tuercas, arandelas</t>
+          <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
         </is>
       </c>
       <c r="E41" s="88" t="n"/>
       <c r="F41" s="88" t="n"/>
       <c r="G41" s="87" t="inlineStr">
         <is>
-          <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+          <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
         </is>
       </c>
       <c r="H41" s="88" t="n"/>
       <c r="I41" s="87" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" s="87" t="inlineStr">
         <is>
-          <t>Suministro nacional genérico A4</t>
+          <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
         </is>
       </c>
       <c r="K41" s="88" t="n"/>
       <c r="L41" s="88" t="n"/>
       <c r="M41" s="87" t="inlineStr">
         <is>
-          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+          <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
         </is>
       </c>
       <c r="N41" s="88" t="n"/>
       <c r="O41" s="88" t="n"/>
     </row>
-    <row r="42" ht="360" customHeight="1">
+    <row r="42" ht="570" customHeight="1">
       <c r="A42" s="87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" s="87" t="inlineStr">
         <is>
-          <t>Conexión flexible ventilador-pasamuros</t>
+          <t>Motor del ventilador (integrado en el cubo)</t>
         </is>
       </c>
       <c r="C42" s="88" t="n"/>
       <c r="D42" s="87" t="inlineStr">
         <is>
-          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
+          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
         </is>
       </c>
       <c r="E42" s="88" t="n"/>
       <c r="F42" s="88" t="n"/>
       <c r="G42" s="87" t="inlineStr">
         <is>
-          <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
+          <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
         </is>
       </c>
       <c r="H42" s="88" t="n"/>
@@ -4537,341 +4243,658 @@
       </c>
       <c r="J42" s="87" t="inlineStr">
         <is>
-          <t>Hardcast Hypalon; Proco serie 500</t>
+          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
         </is>
       </c>
       <c r="K42" s="88" t="n"/>
       <c r="L42" s="88" t="n"/>
       <c r="M42" s="87" t="inlineStr">
         <is>
-          <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
+          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
         </is>
       </c>
       <c r="N42" s="88" t="n"/>
       <c r="O42" s="88" t="n"/>
     </row>
-    <row r="43" ht="600" customHeight="1">
+    <row r="43" ht="465" customHeight="1">
       <c r="A43" s="87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B43" s="87" t="inlineStr">
         <is>
-          <t>Selladores</t>
+          <t>Prefiltro (etapa 1)</t>
         </is>
       </c>
       <c r="C43" s="88" t="n"/>
       <c r="D43" s="87" t="inlineStr">
         <is>
-          <t>Sellado de pasamuros, marcos y empalmes</t>
+          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
         </is>
       </c>
       <c r="E43" s="88" t="n"/>
       <c r="F43" s="88" t="n"/>
       <c r="G43" s="87" t="inlineStr">
         <is>
-          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
+          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
         </is>
       </c>
       <c r="H43" s="88" t="n"/>
       <c r="I43" s="87" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>1 (+ repuestos)</t>
         </is>
       </c>
       <c r="J43" s="87" t="inlineStr">
         <is>
-          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
+          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
         </is>
       </c>
       <c r="K43" s="88" t="n"/>
       <c r="L43" s="88" t="n"/>
       <c r="M43" s="87" t="inlineStr">
         <is>
-          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
+          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
       <c r="N43" s="88" t="n"/>
       <c r="O43" s="88" t="n"/>
     </row>
-    <row r="44" ht="240" customHeight="1">
+    <row r="44" ht="660" customHeight="1">
       <c r="A44" s="87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B44" s="87" t="inlineStr">
         <is>
-          <t>Protecciones eléctricas y tablero</t>
+          <t>Filtro final (etapa 2)</t>
         </is>
       </c>
       <c r="C44" s="88" t="n"/>
       <c r="D44" s="87" t="inlineStr">
         <is>
-          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
+          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
         </is>
       </c>
       <c r="E44" s="88" t="n"/>
       <c r="F44" s="88" t="n"/>
       <c r="G44" s="87" t="inlineStr">
         <is>
-          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
+          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
         </is>
       </c>
       <c r="H44" s="88" t="n"/>
       <c r="I44" s="87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 (+ repuestos)</t>
         </is>
       </c>
       <c r="J44" s="87" t="inlineStr">
         <is>
-          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
+          <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
         </is>
       </c>
       <c r="K44" s="88" t="n"/>
       <c r="L44" s="88" t="n"/>
       <c r="M44" s="87" t="inlineStr">
         <is>
-          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
+          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
       <c r="N44" s="88" t="n"/>
       <c r="O44" s="88" t="n"/>
     </row>
-    <row r="45" ht="210" customHeight="1">
+    <row r="45" ht="420" customHeight="1">
       <c r="A45" s="87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B45" s="87" t="inlineStr">
         <is>
-          <t>Cableado y canalización</t>
+          <t>Marcos portafiltros</t>
         </is>
       </c>
       <c r="C45" s="88" t="n"/>
       <c r="D45" s="87" t="inlineStr">
         <is>
-          <t>Circuito de alimentación del motor 0.75 HP</t>
+          <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
         </is>
       </c>
       <c r="E45" s="88" t="n"/>
       <c r="F45" s="88" t="n"/>
       <c r="G45" s="87" t="inlineStr">
         <is>
-          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
+          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
       <c r="H45" s="88" t="n"/>
       <c r="I45" s="87" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>1 juego</t>
         </is>
       </c>
       <c r="J45" s="87" t="inlineStr">
         <is>
-          <t>Suministro nacional certificado RETIE</t>
+          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
       <c r="K45" s="88" t="n"/>
       <c r="L45" s="88" t="n"/>
       <c r="M45" s="87" t="inlineStr">
         <is>
-          <t>Requisito RETIE / NTC 2050</t>
+          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
       <c r="N45" s="88" t="n"/>
       <c r="O45" s="88" t="n"/>
     </row>
-    <row r="46" ht="345" customHeight="1">
+    <row r="46" ht="450" customHeight="1">
       <c r="A46" s="87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B46" s="87" t="inlineStr">
         <is>
-          <t>Caja/housing de filtración y transición</t>
+          <t>Rejillas de descarga</t>
         </is>
       </c>
       <c r="C46" s="88" t="n"/>
       <c r="D46" s="87" t="inlineStr">
         <is>
-          <t>Alojar portafiltros, malla anti-insectos y adaptar la boca cuadrada 24×24 in del filtro a la boca circular del ventilador axial</t>
+          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
       <c r="E46" s="88" t="n"/>
       <c r="F46" s="88" t="n"/>
       <c r="G46" s="87" t="inlineStr">
         <is>
-          <t>Inox 316L o PRFV viniléster (mismo criterio anticorrosivo del ventilador); tapas de inspección, juntas PU</t>
+          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
       <c r="H46" s="88" t="n"/>
       <c r="I46" s="87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" s="87" t="inlineStr">
         <is>
-          <t>Fabricación local a partir de planos del submittal del ventilador</t>
+          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
       <c r="K46" s="88" t="n"/>
       <c r="L46" s="88" t="n"/>
       <c r="M46" s="87" t="inlineStr">
         <is>
-          <t>Derivado de HD-FILT-001 §7.3</t>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N46" s="88" t="n"/>
       <c r="O46" s="88" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1"/>
-    <row r="48" ht="15" customHeight="1"/>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="84" t="inlineStr">
-        <is>
-          <t>3. Notas de suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="165" customHeight="1">
-      <c r="A50" s="83" t="inlineStr">
-        <is>
-          <t>3.1. Los ítems 1, 4 y 13 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1), la potencia definitiva del motor (ítem 2) y las dimensiones de la caja de filtración/transición cuadrado-circular (ítem 13) se confirman con el software o planos del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1"/>
-    <row r="52" ht="15" customHeight="1"/>
-    <row r="53" ht="15" customHeight="1"/>
+    <row r="47" ht="375" customHeight="1">
+      <c r="A47" s="87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B47" s="87" t="inlineStr">
+        <is>
+          <t>Malla anti-insectos</t>
+        </is>
+      </c>
+      <c r="C47" s="88" t="n"/>
+      <c r="D47" s="87" t="inlineStr">
+        <is>
+          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
+        </is>
+      </c>
+      <c r="E47" s="88" t="n"/>
+      <c r="F47" s="88" t="n"/>
+      <c r="G47" s="87" t="inlineStr">
+        <is>
+          <t>Inox 316</t>
+        </is>
+      </c>
+      <c r="H47" s="88" t="n"/>
+      <c r="I47" s="87" t="inlineStr">
+        <is>
+          <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
+        </is>
+      </c>
+      <c r="J47" s="87" t="inlineStr">
+        <is>
+          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
+        </is>
+      </c>
+      <c r="K47" s="88" t="n"/>
+      <c r="L47" s="88" t="n"/>
+      <c r="M47" s="87" t="inlineStr">
+        <is>
+          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
+        </is>
+      </c>
+      <c r="N47" s="88" t="n"/>
+      <c r="O47" s="88" t="n"/>
+    </row>
+    <row r="48" ht="435" customHeight="1">
+      <c r="A48" s="87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B48" s="87" t="inlineStr">
+        <is>
+          <t>Estructura de unión y soportes</t>
+        </is>
+      </c>
+      <c r="C48" s="88" t="n"/>
+      <c r="D48" s="87" t="inlineStr">
+        <is>
+          <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
+        </is>
+      </c>
+      <c r="E48" s="88" t="n"/>
+      <c r="F48" s="88" t="n"/>
+      <c r="G48" s="87" t="inlineStr">
+        <is>
+          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+        </is>
+      </c>
+      <c r="H48" s="88" t="n"/>
+      <c r="I48" s="87" t="inlineStr">
+        <is>
+          <t>1 + Lote</t>
+        </is>
+      </c>
+      <c r="J48" s="87" t="inlineStr">
+        <is>
+          <t>Fabricación local a partir de planos del submittal del ventilador</t>
+        </is>
+      </c>
+      <c r="K48" s="88" t="n"/>
+      <c r="L48" s="88" t="n"/>
+      <c r="M48" s="87" t="inlineStr">
+        <is>
+          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+        </is>
+      </c>
+      <c r="N48" s="88" t="n"/>
+      <c r="O48" s="88" t="n"/>
+    </row>
+    <row r="49" ht="525" customHeight="1">
+      <c r="A49" s="87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B49" s="87" t="inlineStr">
+        <is>
+          <t>Cubierta intemperie</t>
+        </is>
+      </c>
+      <c r="C49" s="88" t="n"/>
+      <c r="D49" s="87" t="inlineStr">
+        <is>
+          <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
+        </is>
+      </c>
+      <c r="E49" s="88" t="n"/>
+      <c r="F49" s="88" t="n"/>
+      <c r="G49" s="87" t="inlineStr">
+        <is>
+          <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
+        </is>
+      </c>
+      <c r="H49" s="88" t="n"/>
+      <c r="I49" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" s="87" t="inlineStr">
+        <is>
+          <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
+        </is>
+      </c>
+      <c r="K49" s="88" t="n"/>
+      <c r="L49" s="88" t="n"/>
+      <c r="M49" s="87" t="inlineStr">
+        <is>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
+        </is>
+      </c>
+      <c r="N49" s="88" t="n"/>
+      <c r="O49" s="88" t="n"/>
+    </row>
+    <row r="50" ht="270" customHeight="1">
+      <c r="A50" s="87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B50" s="87" t="inlineStr">
+        <is>
+          <t>Malla de protección interior</t>
+        </is>
+      </c>
+      <c r="C50" s="88" t="n"/>
+      <c r="D50" s="87" t="inlineStr">
+        <is>
+          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
+        </is>
+      </c>
+      <c r="E50" s="88" t="n"/>
+      <c r="F50" s="88" t="n"/>
+      <c r="G50" s="87" t="inlineStr">
+        <is>
+          <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
+        </is>
+      </c>
+      <c r="H50" s="88" t="n"/>
+      <c r="I50" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" s="87" t="inlineStr">
+        <is>
+          <t>Fabricación local según submittal</t>
+        </is>
+      </c>
+      <c r="K50" s="88" t="n"/>
+      <c r="L50" s="88" t="n"/>
+      <c r="M50" s="87" t="inlineStr">
+        <is>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
+        </is>
+      </c>
+      <c r="N50" s="88" t="n"/>
+      <c r="O50" s="88" t="n"/>
+    </row>
+    <row r="51" ht="600" customHeight="1">
+      <c r="A51" s="87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="87" t="inlineStr">
+        <is>
+          <t>Selladores</t>
+        </is>
+      </c>
+      <c r="C51" s="88" t="n"/>
+      <c r="D51" s="87" t="inlineStr">
+        <is>
+          <t>Sellado de pasamuros, marcos y empalmes</t>
+        </is>
+      </c>
+      <c r="E51" s="88" t="n"/>
+      <c r="F51" s="88" t="n"/>
+      <c r="G51" s="87" t="inlineStr">
+        <is>
+          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
+        </is>
+      </c>
+      <c r="H51" s="88" t="n"/>
+      <c r="I51" s="87" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="J51" s="87" t="inlineStr">
+        <is>
+          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
+        </is>
+      </c>
+      <c r="K51" s="88" t="n"/>
+      <c r="L51" s="88" t="n"/>
+      <c r="M51" s="87" t="inlineStr">
+        <is>
+          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
+        </is>
+      </c>
+      <c r="N51" s="88" t="n"/>
+      <c r="O51" s="88" t="n"/>
+    </row>
+    <row r="52" ht="240" customHeight="1">
+      <c r="A52" s="87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B52" s="87" t="inlineStr">
+        <is>
+          <t>Protecciones eléctricas y tablero</t>
+        </is>
+      </c>
+      <c r="C52" s="88" t="n"/>
+      <c r="D52" s="87" t="inlineStr">
+        <is>
+          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
+        </is>
+      </c>
+      <c r="E52" s="88" t="n"/>
+      <c r="F52" s="88" t="n"/>
+      <c r="G52" s="87" t="inlineStr">
+        <is>
+          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
+        </is>
+      </c>
+      <c r="H52" s="88" t="n"/>
+      <c r="I52" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" s="87" t="inlineStr">
+        <is>
+          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
+        </is>
+      </c>
+      <c r="K52" s="88" t="n"/>
+      <c r="L52" s="88" t="n"/>
+      <c r="M52" s="87" t="inlineStr">
+        <is>
+          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
+        </is>
+      </c>
+      <c r="N52" s="88" t="n"/>
+      <c r="O52" s="88" t="n"/>
+    </row>
+    <row r="53" ht="210" customHeight="1">
+      <c r="A53" s="87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B53" s="87" t="inlineStr">
+        <is>
+          <t>Cableado y canalización</t>
+        </is>
+      </c>
+      <c r="C53" s="88" t="n"/>
+      <c r="D53" s="87" t="inlineStr">
+        <is>
+          <t>Circuito de alimentación del motor 0.75 HP</t>
+        </is>
+      </c>
+      <c r="E53" s="88" t="n"/>
+      <c r="F53" s="88" t="n"/>
+      <c r="G53" s="87" t="inlineStr">
+        <is>
+          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
+        </is>
+      </c>
+      <c r="H53" s="88" t="n"/>
+      <c r="I53" s="87" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="J53" s="87" t="inlineStr">
+        <is>
+          <t>Suministro nacional certificado RETIE</t>
+        </is>
+      </c>
+      <c r="K53" s="88" t="n"/>
+      <c r="L53" s="88" t="n"/>
+      <c r="M53" s="87" t="inlineStr">
+        <is>
+          <t>Requisito RETIE / NTC 2050</t>
+        </is>
+      </c>
+      <c r="N53" s="88" t="n"/>
+      <c r="O53" s="88" t="n"/>
+    </row>
     <row r="54" ht="15" customHeight="1"/>
     <row r="55" ht="15" customHeight="1"/>
-    <row r="56" ht="150" customHeight="1">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1"/>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="84" t="inlineStr">
+        <is>
+          <t>3. Notas de suministro</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="165" customHeight="1">
+      <c r="A57" s="83" t="inlineStr">
+        <is>
+          <t>3.1. Los ítems 1, 4, 8 y 9 requieren cotización formal con submittal: la selección final de RPM del ventilador mural Ø560 mm (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar; las dimensiones de la estructura de unión (ítem 8) y de la cubierta intemperie (ítem 9) se definen con los planos del submittal del ventilador.</t>
+        </is>
+      </c>
+    </row>
     <row r="58" ht="15" customHeight="1"/>
     <row r="59" ht="15" customHeight="1"/>
     <row r="60" ht="15" customHeight="1"/>
     <row r="61" ht="15" customHeight="1"/>
     <row r="62" ht="15" customHeight="1"/>
-    <row r="63" ht="165" customHeight="1">
-      <c r="A63" s="83" t="inlineStr">
-        <is>
-          <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1"/>
+    <row r="63" ht="15" customHeight="1"/>
+    <row r="64" ht="150" customHeight="1">
+      <c r="A64" s="83" t="inlineStr">
+        <is>
+          <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
     <row r="65" ht="15" customHeight="1"/>
     <row r="66" ht="15" customHeight="1"/>
     <row r="67" ht="15" customHeight="1"/>
+    <row r="68" ht="15" customHeight="1"/>
+    <row r="69" ht="15" customHeight="1"/>
+    <row r="70" ht="15" customHeight="1"/>
+    <row r="71" ht="165" customHeight="1">
+      <c r="A71" s="83" t="inlineStr">
+        <is>
+          <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1"/>
+    <row r="73" ht="15" customHeight="1"/>
+    <row r="74" ht="15" customHeight="1"/>
+    <row r="75" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="96">
     <mergeCell ref="M40:O40"/>
-    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D47:F47"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="M41:O41"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="J50:L50"/>
     <mergeCell ref="C2:L3"/>
+    <mergeCell ref="A29:O29"/>
     <mergeCell ref="J46:L46"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="A18:O24"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="J48:L48"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A50:O55"/>
-    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="M52:O52"/>
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B1:B5"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="A10:O11"/>
-    <mergeCell ref="A23:O28"/>
+    <mergeCell ref="G48:H48"/>
     <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A25:O27"/>
     <mergeCell ref="J41:L41"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="G38:H38"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A18:O20"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="G49:H49"/>
     <mergeCell ref="J42:L42"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="M43:O43"/>
     <mergeCell ref="J44:L44"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J37:L37"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="D40:F40"/>
-    <mergeCell ref="M35:O35"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="A13:O14"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="A64:O70"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A38:O39"/>
+    <mergeCell ref="A56:O56"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="A31:O32"/>
     <mergeCell ref="M42:O42"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="J47:L47"/>
     <mergeCell ref="A8:O8"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="A56:O62"/>
     <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A63:O67"/>
+    <mergeCell ref="A71:O75"/>
+    <mergeCell ref="A30:O35"/>
+    <mergeCell ref="D50:F50"/>
     <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A57:O63"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="D34:F34"/>
     <mergeCell ref="M44:O44"/>
+    <mergeCell ref="G51:H51"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G50:H50"/>
     <mergeCell ref="D45:F45"/>
-    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="M51:O51"/>
     <mergeCell ref="G43:H43"/>
-    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="G52:H52"/>
     <mergeCell ref="J45:L45"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="M45:O45"/>
+    <mergeCell ref="G53:H53"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="J51:L51"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M50:O50"/>
     <mergeCell ref="G45:H45"/>
-    <mergeCell ref="M34:O34"/>
     <mergeCell ref="A15:O17"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="G47:H47"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="A49:O49"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="M48:O48"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="G40:H40"/>
+    <mergeCell ref="D49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Emisiones/4.0 HV-LISTADOS/P2437-HV-LIS-001.xlsx
+++ b/Emisiones/4.0 HV-LISTADOS/P2437-HV-LIS-001.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -164,29 +164,17 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
+      <color rgb="00375623"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -237,8 +225,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -395,7 +383,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -513,12 +501,12 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -541,25 +529,25 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -585,22 +573,19 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3718,38 +3703,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
@@ -3757,8 +3739,8 @@
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
@@ -3766,34 +3748,6 @@
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="13" customWidth="1" min="49" max="49"/>
-    <col width="13" customWidth="1" min="50" max="50"/>
-    <col width="13" customWidth="1" min="51" max="51"/>
-    <col width="13" customWidth="1" min="52" max="52"/>
-    <col width="13" customWidth="1" min="53" max="53"/>
-    <col width="13" customWidth="1" min="56" max="56"/>
-    <col width="13" customWidth="1" min="57" max="57"/>
-    <col width="13" customWidth="1" min="58" max="58"/>
-    <col width="13" customWidth="1" min="59" max="59"/>
-    <col width="13" customWidth="1" min="60" max="60"/>
-    <col width="13" customWidth="1" min="61" max="61"/>
-    <col width="13" customWidth="1" min="62" max="62"/>
-    <col width="13" customWidth="1" min="63" max="63"/>
-    <col width="13" customWidth="1" min="64" max="64"/>
-    <col width="13" customWidth="1" min="65" max="65"/>
-    <col width="13" customWidth="1" min="66" max="66"/>
-    <col width="13" customWidth="1" min="67" max="67"/>
-    <col width="13" customWidth="1" min="68" max="68"/>
-    <col width="13" customWidth="1" min="69" max="69"/>
-    <col width="13" customWidth="1" min="70" max="70"/>
-    <col width="13" customWidth="1" min="71" max="71"/>
-    <col width="13" customWidth="1" min="72" max="72"/>
-    <col width="13" customWidth="1" min="73" max="73"/>
-    <col width="13" customWidth="1" min="74" max="74"/>
-    <col width="13" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4003,7 +3957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="38" customHeight="1">
       <c r="A8" s="81" t="inlineStr">
         <is>
           <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
@@ -4024,879 +3978,845 @@
       <c r="N8" s="55" t="n"/>
       <c r="O8" s="55" t="n"/>
     </row>
-    <row r="9" ht="450" customHeight="1">
+    <row r="9" ht="266" customHeight="1">
       <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Listado de equipos y materiales (BOQ): sistema de ventilación del laboratorio</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="210" customHeight="1">
+    <row r="10" ht="76" customHeight="1">
       <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Proyecto: P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá (Cundinamarca)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1"/>
-    <row r="12" ht="60" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="83" t="inlineStr">
+        <is>
+          <t>Documento: listado_equipos.md — Revisión 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
-          <t>Documento: listado_equipos.md — Revisión 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="195" customHeight="1">
+          <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="114" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
-          <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1"/>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="83" t="inlineStr">
-        <is>
           <t>Base: informe_investigacion.md (misma revisión); punto de diseño 3 840 m³/h @ 165 Pa en el sitio (225 Pa equivalente de catálogo, ρ = 1.2 kg/m³).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="165" customHeight="1">
-      <c r="A18" s="83" t="inlineStr">
+    <row r="14" ht="456" customHeight="1">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png): ventilador axial mural Ø560 mm de transmisión directa, banco de filtración alojado en la cubierta intemperie, estructura de unión pernada al muro y malla de protección interior. Se eliminan la conexión flexible y la caja/housing con transición cuadrado/circular (REV1).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1"/>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="83" t="inlineStr">
+    <row r="15" ht="38" customHeight="1"/>
+    <row r="16" ht="114" customHeight="1">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1"/>
-    <row r="27" ht="15" customHeight="1"/>
-    <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="75" customHeight="1">
-      <c r="A29" s="84" t="inlineStr">
+    <row r="17" ht="38" customHeight="1"/>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="82" t="inlineStr">
         <is>
           <t>1. Alcance del suministro</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="83" t="inlineStr">
+    <row r="19" ht="418" customHeight="1">
+      <c r="A19" s="83" t="inlineStr">
         <is>
           <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="84" t="inlineStr">
+    <row r="20" ht="38" customHeight="1"/>
+    <row r="21" ht="38" customHeight="1"/>
+    <row r="22" ht="114" customHeight="1">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="135" customHeight="1">
-      <c r="A38" s="85" t="inlineStr">
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="120" customHeight="1">
-      <c r="A40" s="86" t="inlineStr">
+    <row r="24" ht="114" customHeight="1">
+      <c r="A24" s="85" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B40" s="86" t="inlineStr">
+      <c r="B24" s="85" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C40" s="86" t="n"/>
-      <c r="D40" s="86" t="inlineStr">
+      <c r="C24" s="85" t="n"/>
+      <c r="D24" s="85" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E40" s="86" t="n"/>
-      <c r="F40" s="86" t="n"/>
-      <c r="G40" s="86" t="inlineStr">
+      <c r="E24" s="85" t="n"/>
+      <c r="F24" s="85" t="n"/>
+      <c r="G24" s="85" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H40" s="86" t="n"/>
-      <c r="I40" s="86" t="inlineStr">
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J40" s="86" t="inlineStr">
+      <c r="J24" s="85" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K40" s="86" t="n"/>
-      <c r="L40" s="86" t="n"/>
-      <c r="M40" s="86" t="inlineStr">
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N40" s="86" t="n"/>
-      <c r="O40" s="86" t="n"/>
-    </row>
-    <row r="41" ht="510" customHeight="1">
-      <c r="A41" s="87" t="inlineStr">
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+    </row>
+    <row r="25" ht="532" customHeight="1">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B41" s="87" t="inlineStr">
+      <c r="B25" s="86" t="inlineStr">
         <is>
           <t>Ventilador de inyección</t>
         </is>
       </c>
-      <c r="C41" s="88" t="n"/>
-      <c r="D41" s="87" t="inlineStr">
+      <c r="C25" s="87" t="n"/>
+      <c r="D25" s="86" t="inlineStr">
         <is>
           <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
         </is>
       </c>
-      <c r="E41" s="88" t="n"/>
-      <c r="F41" s="88" t="n"/>
-      <c r="G41" s="87" t="inlineStr">
+      <c r="E25" s="87" t="n"/>
+      <c r="F25" s="87" t="n"/>
+      <c r="G25" s="86" t="inlineStr">
         <is>
           <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
         </is>
       </c>
-      <c r="H41" s="88" t="n"/>
-      <c r="I41" s="87" t="inlineStr">
+      <c r="H25" s="87" t="n"/>
+      <c r="I25" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J41" s="87" t="inlineStr">
+      <c r="J25" s="86" t="inlineStr">
         <is>
           <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
         </is>
       </c>
-      <c r="K41" s="88" t="n"/>
-      <c r="L41" s="88" t="n"/>
-      <c r="M41" s="87" t="inlineStr">
+      <c r="K25" s="87" t="n"/>
+      <c r="L25" s="87" t="n"/>
+      <c r="M25" s="86" t="inlineStr">
         <is>
           <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
         </is>
       </c>
-      <c r="N41" s="88" t="n"/>
-      <c r="O41" s="88" t="n"/>
-    </row>
-    <row r="42" ht="570" customHeight="1">
-      <c r="A42" s="87" t="inlineStr">
+      <c r="N25" s="87" t="n"/>
+      <c r="O25" s="87" t="n"/>
+    </row>
+    <row r="26" ht="570" customHeight="1">
+      <c r="A26" s="86" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B42" s="87" t="inlineStr">
+      <c r="B26" s="86" t="inlineStr">
         <is>
           <t>Motor del ventilador (integrado en el cubo)</t>
         </is>
       </c>
-      <c r="C42" s="88" t="n"/>
-      <c r="D42" s="87" t="inlineStr">
+      <c r="C26" s="87" t="n"/>
+      <c r="D26" s="86" t="inlineStr">
         <is>
           <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
         </is>
       </c>
-      <c r="E42" s="88" t="n"/>
-      <c r="F42" s="88" t="n"/>
-      <c r="G42" s="87" t="inlineStr">
+      <c r="E26" s="87" t="n"/>
+      <c r="F26" s="87" t="n"/>
+      <c r="G26" s="86" t="inlineStr">
         <is>
           <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
         </is>
       </c>
-      <c r="H42" s="88" t="n"/>
-      <c r="I42" s="87" t="inlineStr">
+      <c r="H26" s="87" t="n"/>
+      <c r="I26" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J42" s="87" t="inlineStr">
+      <c r="J26" s="86" t="inlineStr">
         <is>
           <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
         </is>
       </c>
-      <c r="K42" s="88" t="n"/>
-      <c r="L42" s="88" t="n"/>
-      <c r="M42" s="87" t="inlineStr">
+      <c r="K26" s="87" t="n"/>
+      <c r="L26" s="87" t="n"/>
+      <c r="M26" s="86" t="inlineStr">
         <is>
           <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
         </is>
       </c>
-      <c r="N42" s="88" t="n"/>
-      <c r="O42" s="88" t="n"/>
-    </row>
-    <row r="43" ht="465" customHeight="1">
-      <c r="A43" s="87" t="inlineStr">
+      <c r="N26" s="87" t="n"/>
+      <c r="O26" s="87" t="n"/>
+    </row>
+    <row r="27" ht="456" customHeight="1">
+      <c r="A27" s="86" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B43" s="87" t="inlineStr">
+      <c r="B27" s="86" t="inlineStr">
         <is>
           <t>Prefiltro (etapa 1)</t>
         </is>
       </c>
-      <c r="C43" s="88" t="n"/>
-      <c r="D43" s="87" t="inlineStr">
+      <c r="C27" s="87" t="n"/>
+      <c r="D27" s="86" t="inlineStr">
         <is>
           <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
         </is>
       </c>
-      <c r="E43" s="88" t="n"/>
-      <c r="F43" s="88" t="n"/>
-      <c r="G43" s="87" t="inlineStr">
+      <c r="E27" s="87" t="n"/>
+      <c r="F27" s="87" t="n"/>
+      <c r="G27" s="86" t="inlineStr">
         <is>
           <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
         </is>
       </c>
-      <c r="H43" s="88" t="n"/>
-      <c r="I43" s="87" t="inlineStr">
+      <c r="H27" s="87" t="n"/>
+      <c r="I27" s="86" t="inlineStr">
         <is>
           <t>1 (+ repuestos)</t>
         </is>
       </c>
-      <c r="J43" s="87" t="inlineStr">
+      <c r="J27" s="86" t="inlineStr">
         <is>
           <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
         </is>
       </c>
-      <c r="K43" s="88" t="n"/>
-      <c r="L43" s="88" t="n"/>
-      <c r="M43" s="87" t="inlineStr">
+      <c r="K27" s="87" t="n"/>
+      <c r="L27" s="87" t="n"/>
+      <c r="M27" s="86" t="inlineStr">
         <is>
           <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
-      <c r="N43" s="88" t="n"/>
-      <c r="O43" s="88" t="n"/>
-    </row>
-    <row r="44" ht="660" customHeight="1">
-      <c r="A44" s="87" t="inlineStr">
+      <c r="N27" s="87" t="n"/>
+      <c r="O27" s="87" t="n"/>
+    </row>
+    <row r="28" ht="684" customHeight="1">
+      <c r="A28" s="86" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B44" s="87" t="inlineStr">
+      <c r="B28" s="86" t="inlineStr">
         <is>
           <t>Filtro final (etapa 2)</t>
         </is>
       </c>
-      <c r="C44" s="88" t="n"/>
-      <c r="D44" s="87" t="inlineStr">
+      <c r="C28" s="87" t="n"/>
+      <c r="D28" s="86" t="inlineStr">
         <is>
           <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
         </is>
       </c>
-      <c r="E44" s="88" t="n"/>
-      <c r="F44" s="88" t="n"/>
-      <c r="G44" s="87" t="inlineStr">
+      <c r="E28" s="87" t="n"/>
+      <c r="F28" s="87" t="n"/>
+      <c r="G28" s="86" t="inlineStr">
         <is>
           <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
         </is>
       </c>
-      <c r="H44" s="88" t="n"/>
-      <c r="I44" s="87" t="inlineStr">
+      <c r="H28" s="87" t="n"/>
+      <c r="I28" s="86" t="inlineStr">
         <is>
           <t>1 (+ repuestos)</t>
         </is>
       </c>
-      <c r="J44" s="87" t="inlineStr">
+      <c r="J28" s="86" t="inlineStr">
         <is>
           <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
         </is>
       </c>
-      <c r="K44" s="88" t="n"/>
-      <c r="L44" s="88" t="n"/>
-      <c r="M44" s="87" t="inlineStr">
+      <c r="K28" s="87" t="n"/>
+      <c r="L28" s="87" t="n"/>
+      <c r="M28" s="86" t="inlineStr">
         <is>
           <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
-      <c r="N44" s="88" t="n"/>
-      <c r="O44" s="88" t="n"/>
-    </row>
-    <row r="45" ht="420" customHeight="1">
-      <c r="A45" s="87" t="inlineStr">
+      <c r="N28" s="87" t="n"/>
+      <c r="O28" s="87" t="n"/>
+    </row>
+    <row r="29" ht="418" customHeight="1">
+      <c r="A29" s="86" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B45" s="87" t="inlineStr">
+      <c r="B29" s="86" t="inlineStr">
         <is>
           <t>Marcos portafiltros</t>
         </is>
       </c>
-      <c r="C45" s="88" t="n"/>
-      <c r="D45" s="87" t="inlineStr">
+      <c r="C29" s="87" t="n"/>
+      <c r="D29" s="86" t="inlineStr">
         <is>
           <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
         </is>
       </c>
-      <c r="E45" s="88" t="n"/>
-      <c r="F45" s="88" t="n"/>
-      <c r="G45" s="87" t="inlineStr">
+      <c r="E29" s="87" t="n"/>
+      <c r="F29" s="87" t="n"/>
+      <c r="G29" s="86" t="inlineStr">
         <is>
           <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
-      <c r="H45" s="88" t="n"/>
-      <c r="I45" s="87" t="inlineStr">
+      <c r="H29" s="87" t="n"/>
+      <c r="I29" s="86" t="inlineStr">
         <is>
           <t>1 juego</t>
         </is>
       </c>
-      <c r="J45" s="87" t="inlineStr">
+      <c r="J29" s="86" t="inlineStr">
         <is>
           <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
-      <c r="K45" s="88" t="n"/>
-      <c r="L45" s="88" t="n"/>
-      <c r="M45" s="87" t="inlineStr">
+      <c r="K29" s="87" t="n"/>
+      <c r="L29" s="87" t="n"/>
+      <c r="M29" s="86" t="inlineStr">
         <is>
           <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
-      <c r="N45" s="88" t="n"/>
-      <c r="O45" s="88" t="n"/>
-    </row>
-    <row r="46" ht="450" customHeight="1">
-      <c r="A46" s="87" t="inlineStr">
+      <c r="N29" s="87" t="n"/>
+      <c r="O29" s="87" t="n"/>
+    </row>
+    <row r="30" ht="456" customHeight="1">
+      <c r="A30" s="86" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B46" s="87" t="inlineStr">
+      <c r="B30" s="86" t="inlineStr">
         <is>
           <t>Rejillas de descarga</t>
         </is>
       </c>
-      <c r="C46" s="88" t="n"/>
-      <c r="D46" s="87" t="inlineStr">
+      <c r="C30" s="87" t="n"/>
+      <c r="D30" s="86" t="inlineStr">
         <is>
           <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
-      <c r="E46" s="88" t="n"/>
-      <c r="F46" s="88" t="n"/>
-      <c r="G46" s="87" t="inlineStr">
+      <c r="E30" s="87" t="n"/>
+      <c r="F30" s="87" t="n"/>
+      <c r="G30" s="86" t="inlineStr">
         <is>
           <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
-      <c r="H46" s="88" t="n"/>
-      <c r="I46" s="87" t="inlineStr">
+      <c r="H30" s="87" t="n"/>
+      <c r="I30" s="86" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J46" s="87" t="inlineStr">
+      <c r="J30" s="86" t="inlineStr">
         <is>
           <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
-      <c r="K46" s="88" t="n"/>
-      <c r="L46" s="88" t="n"/>
-      <c r="M46" s="87" t="inlineStr">
+      <c r="K30" s="87" t="n"/>
+      <c r="L30" s="87" t="n"/>
+      <c r="M30" s="86" t="inlineStr">
         <is>
           <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
-      <c r="N46" s="88" t="n"/>
-      <c r="O46" s="88" t="n"/>
-    </row>
-    <row r="47" ht="375" customHeight="1">
-      <c r="A47" s="87" t="inlineStr">
+      <c r="N30" s="87" t="n"/>
+      <c r="O30" s="87" t="n"/>
+    </row>
+    <row r="31" ht="380" customHeight="1">
+      <c r="A31" s="86" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B47" s="87" t="inlineStr">
+      <c r="B31" s="86" t="inlineStr">
         <is>
           <t>Malla anti-insectos</t>
         </is>
       </c>
-      <c r="C47" s="88" t="n"/>
-      <c r="D47" s="87" t="inlineStr">
+      <c r="C31" s="87" t="n"/>
+      <c r="D31" s="86" t="inlineStr">
         <is>
           <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
         </is>
       </c>
-      <c r="E47" s="88" t="n"/>
-      <c r="F47" s="88" t="n"/>
-      <c r="G47" s="87" t="inlineStr">
+      <c r="E31" s="87" t="n"/>
+      <c r="F31" s="87" t="n"/>
+      <c r="G31" s="86" t="inlineStr">
         <is>
           <t>Inox 316</t>
         </is>
       </c>
-      <c r="H47" s="88" t="n"/>
-      <c r="I47" s="87" t="inlineStr">
+      <c r="H31" s="87" t="n"/>
+      <c r="I31" s="86" t="inlineStr">
         <is>
           <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
         </is>
       </c>
-      <c r="J47" s="87" t="inlineStr">
+      <c r="J31" s="86" t="inlineStr">
         <is>
           <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
         </is>
       </c>
-      <c r="K47" s="88" t="n"/>
-      <c r="L47" s="88" t="n"/>
-      <c r="M47" s="87" t="inlineStr">
+      <c r="K31" s="87" t="n"/>
+      <c r="L31" s="87" t="n"/>
+      <c r="M31" s="86" t="inlineStr">
         <is>
           <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
         </is>
       </c>
-      <c r="N47" s="88" t="n"/>
-      <c r="O47" s="88" t="n"/>
-    </row>
-    <row r="48" ht="435" customHeight="1">
-      <c r="A48" s="87" t="inlineStr">
+      <c r="N31" s="87" t="n"/>
+      <c r="O31" s="87" t="n"/>
+    </row>
+    <row r="32" ht="456" customHeight="1">
+      <c r="A32" s="86" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B48" s="87" t="inlineStr">
+      <c r="B32" s="86" t="inlineStr">
         <is>
           <t>Estructura de unión y soportes</t>
         </is>
       </c>
-      <c r="C48" s="88" t="n"/>
-      <c r="D48" s="87" t="inlineStr">
+      <c r="C32" s="87" t="n"/>
+      <c r="D32" s="86" t="inlineStr">
         <is>
           <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
         </is>
       </c>
-      <c r="E48" s="88" t="n"/>
-      <c r="F48" s="88" t="n"/>
-      <c r="G48" s="87" t="inlineStr">
+      <c r="E32" s="87" t="n"/>
+      <c r="F32" s="87" t="n"/>
+      <c r="G32" s="86" t="inlineStr">
         <is>
           <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
         </is>
       </c>
-      <c r="H48" s="88" t="n"/>
-      <c r="I48" s="87" t="inlineStr">
+      <c r="H32" s="87" t="n"/>
+      <c r="I32" s="86" t="inlineStr">
         <is>
           <t>1 + Lote</t>
         </is>
       </c>
-      <c r="J48" s="87" t="inlineStr">
+      <c r="J32" s="86" t="inlineStr">
         <is>
           <t>Fabricación local a partir de planos del submittal del ventilador</t>
         </is>
       </c>
-      <c r="K48" s="88" t="n"/>
-      <c r="L48" s="88" t="n"/>
-      <c r="M48" s="87" t="inlineStr">
+      <c r="K32" s="87" t="n"/>
+      <c r="L32" s="87" t="n"/>
+      <c r="M32" s="86" t="inlineStr">
         <is>
           <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
         </is>
       </c>
-      <c r="N48" s="88" t="n"/>
-      <c r="O48" s="88" t="n"/>
-    </row>
-    <row r="49" ht="525" customHeight="1">
-      <c r="A49" s="87" t="inlineStr">
+      <c r="N32" s="87" t="n"/>
+      <c r="O32" s="87" t="n"/>
+    </row>
+    <row r="33" ht="532" customHeight="1">
+      <c r="A33" s="86" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B49" s="87" t="inlineStr">
+      <c r="B33" s="86" t="inlineStr">
         <is>
           <t>Cubierta intemperie</t>
         </is>
       </c>
-      <c r="C49" s="88" t="n"/>
-      <c r="D49" s="87" t="inlineStr">
+      <c r="C33" s="87" t="n"/>
+      <c r="D33" s="86" t="inlineStr">
         <is>
           <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
         </is>
       </c>
-      <c r="E49" s="88" t="n"/>
-      <c r="F49" s="88" t="n"/>
-      <c r="G49" s="87" t="inlineStr">
+      <c r="E33" s="87" t="n"/>
+      <c r="F33" s="87" t="n"/>
+      <c r="G33" s="86" t="inlineStr">
         <is>
           <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
         </is>
       </c>
-      <c r="H49" s="88" t="n"/>
-      <c r="I49" s="87" t="inlineStr">
+      <c r="H33" s="87" t="n"/>
+      <c r="I33" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J49" s="87" t="inlineStr">
+      <c r="J33" s="86" t="inlineStr">
         <is>
           <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
         </is>
       </c>
-      <c r="K49" s="88" t="n"/>
-      <c r="L49" s="88" t="n"/>
-      <c r="M49" s="87" t="inlineStr">
+      <c r="K33" s="87" t="n"/>
+      <c r="L33" s="87" t="n"/>
+      <c r="M33" s="86" t="inlineStr">
         <is>
           <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
-      <c r="N49" s="88" t="n"/>
-      <c r="O49" s="88" t="n"/>
-    </row>
-    <row r="50" ht="270" customHeight="1">
-      <c r="A50" s="87" t="inlineStr">
+      <c r="N33" s="87" t="n"/>
+      <c r="O33" s="87" t="n"/>
+    </row>
+    <row r="34" ht="266" customHeight="1">
+      <c r="A34" s="86" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B50" s="87" t="inlineStr">
+      <c r="B34" s="86" t="inlineStr">
         <is>
           <t>Malla de protección interior</t>
         </is>
       </c>
-      <c r="C50" s="88" t="n"/>
-      <c r="D50" s="87" t="inlineStr">
+      <c r="C34" s="87" t="n"/>
+      <c r="D34" s="86" t="inlineStr">
         <is>
           <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
         </is>
       </c>
-      <c r="E50" s="88" t="n"/>
-      <c r="F50" s="88" t="n"/>
-      <c r="G50" s="87" t="inlineStr">
+      <c r="E34" s="87" t="n"/>
+      <c r="F34" s="87" t="n"/>
+      <c r="G34" s="86" t="inlineStr">
         <is>
           <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
         </is>
       </c>
-      <c r="H50" s="88" t="n"/>
-      <c r="I50" s="87" t="inlineStr">
+      <c r="H34" s="87" t="n"/>
+      <c r="I34" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J50" s="87" t="inlineStr">
+      <c r="J34" s="86" t="inlineStr">
         <is>
           <t>Fabricación local según submittal</t>
         </is>
       </c>
-      <c r="K50" s="88" t="n"/>
-      <c r="L50" s="88" t="n"/>
-      <c r="M50" s="87" t="inlineStr">
+      <c r="K34" s="87" t="n"/>
+      <c r="L34" s="87" t="n"/>
+      <c r="M34" s="86" t="inlineStr">
         <is>
           <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
-      <c r="N50" s="88" t="n"/>
-      <c r="O50" s="88" t="n"/>
-    </row>
-    <row r="51" ht="600" customHeight="1">
-      <c r="A51" s="87" t="inlineStr">
+      <c r="N34" s="87" t="n"/>
+      <c r="O34" s="87" t="n"/>
+    </row>
+    <row r="35" ht="608" customHeight="1">
+      <c r="A35" s="86" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B51" s="87" t="inlineStr">
+      <c r="B35" s="86" t="inlineStr">
         <is>
           <t>Selladores</t>
         </is>
       </c>
-      <c r="C51" s="88" t="n"/>
-      <c r="D51" s="87" t="inlineStr">
+      <c r="C35" s="87" t="n"/>
+      <c r="D35" s="86" t="inlineStr">
         <is>
           <t>Sellado de pasamuros, marcos y empalmes</t>
         </is>
       </c>
-      <c r="E51" s="88" t="n"/>
-      <c r="F51" s="88" t="n"/>
-      <c r="G51" s="87" t="inlineStr">
+      <c r="E35" s="87" t="n"/>
+      <c r="F35" s="87" t="n"/>
+      <c r="G35" s="86" t="inlineStr">
         <is>
           <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
         </is>
       </c>
-      <c r="H51" s="88" t="n"/>
-      <c r="I51" s="87" t="inlineStr">
+      <c r="H35" s="87" t="n"/>
+      <c r="I35" s="86" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="J51" s="87" t="inlineStr">
+      <c r="J35" s="86" t="inlineStr">
         <is>
           <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
         </is>
       </c>
-      <c r="K51" s="88" t="n"/>
-      <c r="L51" s="88" t="n"/>
-      <c r="M51" s="87" t="inlineStr">
+      <c r="K35" s="87" t="n"/>
+      <c r="L35" s="87" t="n"/>
+      <c r="M35" s="86" t="inlineStr">
         <is>
           <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
         </is>
       </c>
-      <c r="N51" s="88" t="n"/>
-      <c r="O51" s="88" t="n"/>
-    </row>
-    <row r="52" ht="240" customHeight="1">
-      <c r="A52" s="87" t="inlineStr">
+      <c r="N35" s="87" t="n"/>
+      <c r="O35" s="87" t="n"/>
+    </row>
+    <row r="36" ht="266" customHeight="1">
+      <c r="A36" s="86" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B52" s="87" t="inlineStr">
+      <c r="B36" s="86" t="inlineStr">
         <is>
           <t>Protecciones eléctricas y tablero</t>
         </is>
       </c>
-      <c r="C52" s="88" t="n"/>
-      <c r="D52" s="87" t="inlineStr">
+      <c r="C36" s="87" t="n"/>
+      <c r="D36" s="86" t="inlineStr">
         <is>
           <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
         </is>
       </c>
-      <c r="E52" s="88" t="n"/>
-      <c r="F52" s="88" t="n"/>
-      <c r="G52" s="87" t="inlineStr">
+      <c r="E36" s="87" t="n"/>
+      <c r="F36" s="87" t="n"/>
+      <c r="G36" s="86" t="inlineStr">
         <is>
           <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
         </is>
       </c>
-      <c r="H52" s="88" t="n"/>
-      <c r="I52" s="87" t="inlineStr">
+      <c r="H36" s="87" t="n"/>
+      <c r="I36" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J52" s="87" t="inlineStr">
+      <c r="J36" s="86" t="inlineStr">
         <is>
           <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
         </is>
       </c>
-      <c r="K52" s="88" t="n"/>
-      <c r="L52" s="88" t="n"/>
-      <c r="M52" s="87" t="inlineStr">
+      <c r="K36" s="87" t="n"/>
+      <c r="L36" s="87" t="n"/>
+      <c r="M36" s="86" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
         </is>
       </c>
-      <c r="N52" s="88" t="n"/>
-      <c r="O52" s="88" t="n"/>
-    </row>
-    <row r="53" ht="210" customHeight="1">
-      <c r="A53" s="87" t="inlineStr">
+      <c r="N36" s="87" t="n"/>
+      <c r="O36" s="87" t="n"/>
+    </row>
+    <row r="37" ht="228" customHeight="1">
+      <c r="A37" s="86" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B53" s="87" t="inlineStr">
+      <c r="B37" s="86" t="inlineStr">
         <is>
           <t>Cableado y canalización</t>
         </is>
       </c>
-      <c r="C53" s="88" t="n"/>
-      <c r="D53" s="87" t="inlineStr">
+      <c r="C37" s="87" t="n"/>
+      <c r="D37" s="86" t="inlineStr">
         <is>
           <t>Circuito de alimentación del motor 0.75 HP</t>
         </is>
       </c>
-      <c r="E53" s="88" t="n"/>
-      <c r="F53" s="88" t="n"/>
-      <c r="G53" s="87" t="inlineStr">
+      <c r="E37" s="87" t="n"/>
+      <c r="F37" s="87" t="n"/>
+      <c r="G37" s="86" t="inlineStr">
         <is>
           <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
         </is>
       </c>
-      <c r="H53" s="88" t="n"/>
-      <c r="I53" s="87" t="inlineStr">
+      <c r="H37" s="87" t="n"/>
+      <c r="I37" s="86" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="J53" s="87" t="inlineStr">
+      <c r="J37" s="86" t="inlineStr">
         <is>
           <t>Suministro nacional certificado RETIE</t>
         </is>
       </c>
-      <c r="K53" s="88" t="n"/>
-      <c r="L53" s="88" t="n"/>
-      <c r="M53" s="87" t="inlineStr">
+      <c r="K37" s="87" t="n"/>
+      <c r="L37" s="87" t="n"/>
+      <c r="M37" s="86" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050</t>
         </is>
       </c>
-      <c r="N53" s="88" t="n"/>
-      <c r="O53" s="88" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1"/>
-    <row r="55" ht="15" customHeight="1"/>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="84" t="inlineStr">
+      <c r="N37" s="87" t="n"/>
+      <c r="O37" s="87" t="n"/>
+    </row>
+    <row r="38" ht="38" customHeight="1"/>
+    <row r="39" ht="76" customHeight="1">
+      <c r="A39" s="82" t="inlineStr">
         <is>
           <t>3. Notas de suministro</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="165" customHeight="1">
-      <c r="A57" s="83" t="inlineStr">
+    <row r="40" ht="570" customHeight="1">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>3.1. Los ítems 1, 4, 8 y 9 requieren cotización formal con submittal: la selección final de RPM del ventilador mural Ø560 mm (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar; las dimensiones de la estructura de unión (ítem 8) y de la cubierta intemperie (ítem 9) se definen con los planos del submittal del ventilador.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1"/>
-    <row r="59" ht="15" customHeight="1"/>
-    <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="15" customHeight="1"/>
-    <row r="62" ht="15" customHeight="1"/>
-    <row r="63" ht="15" customHeight="1"/>
-    <row r="64" ht="150" customHeight="1">
-      <c r="A64" s="83" t="inlineStr">
+    <row r="41" ht="38" customHeight="1"/>
+    <row r="42" ht="532" customHeight="1">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1"/>
-    <row r="66" ht="15" customHeight="1"/>
-    <row r="67" ht="15" customHeight="1"/>
-    <row r="68" ht="15" customHeight="1"/>
-    <row r="69" ht="15" customHeight="1"/>
-    <row r="70" ht="15" customHeight="1"/>
-    <row r="71" ht="165" customHeight="1">
-      <c r="A71" s="83" t="inlineStr">
+    <row r="43" ht="38" customHeight="1"/>
+    <row r="44" ht="418" customHeight="1">
+      <c r="A44" s="83" t="inlineStr">
         <is>
           <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1"/>
-    <row r="73" ht="15" customHeight="1"/>
-    <row r="74" ht="15" customHeight="1"/>
-    <row r="75" ht="15" customHeight="1"/>
+    <row r="45" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="96">
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D47:F47"/>
+  <mergeCells count="91">
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="J25:L25"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="M24:O24"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="A18:O24"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="A10:O11"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A25:O27"/>
-    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A19:O20"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M37:O37"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="J28:L28"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A14:O15"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="J30:L30"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A13:O14"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="A64:O70"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="A38:O39"/>
-    <mergeCell ref="A56:O56"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="A40:O41"/>
+    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A71:O75"/>
-    <mergeCell ref="A30:O35"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A57:O63"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="A42:O43"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A44:O45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="G28:H28"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="J51:L51"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="A15:O17"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="M48:O48"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Emisiones/4.0 HV-LISTADOS/P2437-HV-LIS-001.xlsx
+++ b/Emisiones/4.0 HV-LISTADOS/P2437-HV-LIS-001.xlsx
@@ -3705,28 +3705,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
@@ -3737,17 +3738,7 @@
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -3957,7 +3948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="81" t="inlineStr">
         <is>
           <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
@@ -3978,800 +3969,782 @@
       <c r="N8" s="55" t="n"/>
       <c r="O8" s="55" t="n"/>
     </row>
-    <row r="9" ht="266" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Listado de equipos y materiales (BOQ): sistema de ventilación del laboratorio</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
+    <row r="10" ht="150" customHeight="1">
       <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Proyecto: P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá (Cundinamarca)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="100" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
-          <t>Documento: listado_equipos.md — Revisión 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="76" customHeight="1">
+          <t>Documento: listado_equipos.md — Revisión 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="114" customHeight="1">
+    <row r="13" ht="200" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Base: informe_investigacion.md (misma revisión); punto de diseño 3 840 m³/h @ 165 Pa en el sitio (225 Pa equivalente de catálogo, ρ = 1.2 kg/m³).</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="456" customHeight="1">
-      <c r="A14" s="83" t="inlineStr">
-        <is>
-          <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png): ventilador axial mural Ø560 mm de transmisión directa, banco de filtración alojado en la cubierta intemperie, estructura de unión pernada al muro y malla de protección interior. Se eliminan la conexión flexible y la caja/housing con transición cuadrado/circular (REV1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1"/>
-    <row r="16" ht="114" customHeight="1">
+    <row r="14" ht="50" customHeight="1"/>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>1. Alcance del suministro</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="450" customHeight="1">
       <c r="A16" s="83" t="inlineStr">
         <is>
-          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="38" customHeight="1"/>
-    <row r="18" ht="76" customHeight="1">
+          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1"/>
+    <row r="18" ht="150" customHeight="1">
       <c r="A18" s="82" t="inlineStr">
         <is>
-          <t>1. Alcance del suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="418" customHeight="1">
-      <c r="A19" s="83" t="inlineStr">
-        <is>
-          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="38" customHeight="1"/>
-    <row r="21" ht="38" customHeight="1"/>
-    <row r="22" ht="114" customHeight="1">
-      <c r="A22" s="82" t="inlineStr">
-        <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="76" customHeight="1">
-      <c r="A23" s="84" t="inlineStr">
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="84" t="inlineStr">
         <is>
           <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="114" customHeight="1">
-      <c r="A24" s="85" t="inlineStr">
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="85" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B24" s="85" t="inlineStr">
+      <c r="B20" s="85" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C24" s="85" t="n"/>
-      <c r="D24" s="85" t="inlineStr">
+      <c r="C20" s="85" t="n"/>
+      <c r="D20" s="85" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E24" s="85" t="n"/>
-      <c r="F24" s="85" t="n"/>
-      <c r="G24" s="85" t="inlineStr">
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="85" t="n"/>
+      <c r="G20" s="85" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H24" s="85" t="n"/>
-      <c r="I24" s="85" t="inlineStr">
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J24" s="85" t="inlineStr">
+      <c r="J20" s="85" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K24" s="85" t="n"/>
-      <c r="L24" s="85" t="n"/>
-      <c r="M24" s="85" t="inlineStr">
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N24" s="85" t="n"/>
-      <c r="O24" s="85" t="n"/>
-    </row>
-    <row r="25" ht="532" customHeight="1">
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+    </row>
+    <row r="21" ht="700" customHeight="1">
+      <c r="A21" s="86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="86" t="inlineStr">
+        <is>
+          <t>Ventilador de inyección</t>
+        </is>
+      </c>
+      <c r="C21" s="87" t="n"/>
+      <c r="D21" s="86" t="inlineStr">
+        <is>
+          <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
+        </is>
+      </c>
+      <c r="E21" s="87" t="n"/>
+      <c r="F21" s="87" t="n"/>
+      <c r="G21" s="86" t="inlineStr">
+        <is>
+          <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
+        </is>
+      </c>
+      <c r="H21" s="87" t="n"/>
+      <c r="I21" s="86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" s="86" t="inlineStr">
+        <is>
+          <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
+        </is>
+      </c>
+      <c r="K21" s="87" t="n"/>
+      <c r="L21" s="87" t="n"/>
+      <c r="M21" s="86" t="inlineStr">
+        <is>
+          <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
+        </is>
+      </c>
+      <c r="N21" s="87" t="n"/>
+      <c r="O21" s="87" t="n"/>
+    </row>
+    <row r="22" ht="750" customHeight="1">
+      <c r="A22" s="86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="86" t="inlineStr">
+        <is>
+          <t>Motor del ventilador (integrado en el cubo)</t>
+        </is>
+      </c>
+      <c r="C22" s="87" t="n"/>
+      <c r="D22" s="86" t="inlineStr">
+        <is>
+          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="E22" s="87" t="n"/>
+      <c r="F22" s="87" t="n"/>
+      <c r="G22" s="86" t="inlineStr">
+        <is>
+          <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
+        </is>
+      </c>
+      <c r="H22" s="87" t="n"/>
+      <c r="I22" s="86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="86" t="inlineStr">
+        <is>
+          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
+        </is>
+      </c>
+      <c r="K22" s="87" t="n"/>
+      <c r="L22" s="87" t="n"/>
+      <c r="M22" s="86" t="inlineStr">
+        <is>
+          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
+        </is>
+      </c>
+      <c r="N22" s="87" t="n"/>
+      <c r="O22" s="87" t="n"/>
+    </row>
+    <row r="23" ht="600" customHeight="1">
+      <c r="A23" s="86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="86" t="inlineStr">
+        <is>
+          <t>Prefiltro (etapa 1)</t>
+        </is>
+      </c>
+      <c r="C23" s="87" t="n"/>
+      <c r="D23" s="86" t="inlineStr">
+        <is>
+          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
+        </is>
+      </c>
+      <c r="E23" s="87" t="n"/>
+      <c r="F23" s="87" t="n"/>
+      <c r="G23" s="86" t="inlineStr">
+        <is>
+          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
+        </is>
+      </c>
+      <c r="H23" s="87" t="n"/>
+      <c r="I23" s="86" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
+      <c r="J23" s="86" t="inlineStr">
+        <is>
+          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
+        </is>
+      </c>
+      <c r="K23" s="87" t="n"/>
+      <c r="L23" s="87" t="n"/>
+      <c r="M23" s="86" t="inlineStr">
+        <is>
+          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
+        </is>
+      </c>
+      <c r="N23" s="87" t="n"/>
+      <c r="O23" s="87" t="n"/>
+    </row>
+    <row r="24" ht="900" customHeight="1">
+      <c r="A24" s="86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" s="86" t="inlineStr">
+        <is>
+          <t>Filtro final (etapa 2)</t>
+        </is>
+      </c>
+      <c r="C24" s="87" t="n"/>
+      <c r="D24" s="86" t="inlineStr">
+        <is>
+          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
+        </is>
+      </c>
+      <c r="E24" s="87" t="n"/>
+      <c r="F24" s="87" t="n"/>
+      <c r="G24" s="86" t="inlineStr">
+        <is>
+          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
+        </is>
+      </c>
+      <c r="H24" s="87" t="n"/>
+      <c r="I24" s="86" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
+      <c r="J24" s="86" t="inlineStr">
+        <is>
+          <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
+        </is>
+      </c>
+      <c r="K24" s="87" t="n"/>
+      <c r="L24" s="87" t="n"/>
+      <c r="M24" s="86" t="inlineStr">
+        <is>
+          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
+        </is>
+      </c>
+      <c r="N24" s="87" t="n"/>
+      <c r="O24" s="87" t="n"/>
+    </row>
+    <row r="25" ht="550" customHeight="1">
       <c r="A25" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" s="86" t="inlineStr">
         <is>
-          <t>Ventilador de inyección</t>
+          <t>Marcos portafiltros</t>
         </is>
       </c>
       <c r="C25" s="87" t="n"/>
       <c r="D25" s="86" t="inlineStr">
         <is>
-          <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
+          <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
         </is>
       </c>
       <c r="E25" s="87" t="n"/>
       <c r="F25" s="87" t="n"/>
       <c r="G25" s="86" t="inlineStr">
         <is>
-          <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
+          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
       <c r="H25" s="87" t="n"/>
       <c r="I25" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 juego</t>
         </is>
       </c>
       <c r="J25" s="86" t="inlineStr">
         <is>
-          <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
+          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
       <c r="K25" s="87" t="n"/>
       <c r="L25" s="87" t="n"/>
       <c r="M25" s="86" t="inlineStr">
         <is>
-          <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
+          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
       <c r="N25" s="87" t="n"/>
       <c r="O25" s="87" t="n"/>
     </row>
-    <row r="26" ht="570" customHeight="1">
+    <row r="26" ht="600" customHeight="1">
       <c r="A26" s="86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B26" s="86" t="inlineStr">
         <is>
-          <t>Motor del ventilador (integrado en el cubo)</t>
+          <t>Rejillas de descarga</t>
         </is>
       </c>
       <c r="C26" s="87" t="n"/>
       <c r="D26" s="86" t="inlineStr">
         <is>
-          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
+          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
       <c r="E26" s="87" t="n"/>
       <c r="F26" s="87" t="n"/>
       <c r="G26" s="86" t="inlineStr">
         <is>
-          <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
+          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
       <c r="H26" s="87" t="n"/>
       <c r="I26" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" s="86" t="inlineStr">
         <is>
-          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
+          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
       <c r="K26" s="87" t="n"/>
       <c r="L26" s="87" t="n"/>
       <c r="M26" s="86" t="inlineStr">
         <is>
-          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N26" s="87" t="n"/>
       <c r="O26" s="87" t="n"/>
     </row>
-    <row r="27" ht="456" customHeight="1">
+    <row r="27" ht="500" customHeight="1">
       <c r="A27" s="86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" s="86" t="inlineStr">
         <is>
-          <t>Prefiltro (etapa 1)</t>
+          <t>Malla anti-insectos</t>
         </is>
       </c>
       <c r="C27" s="87" t="n"/>
       <c r="D27" s="86" t="inlineStr">
         <is>
-          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
+          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
         </is>
       </c>
       <c r="E27" s="87" t="n"/>
       <c r="F27" s="87" t="n"/>
       <c r="G27" s="86" t="inlineStr">
         <is>
-          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
+          <t>Inox 316</t>
         </is>
       </c>
       <c r="H27" s="87" t="n"/>
       <c r="I27" s="86" t="inlineStr">
         <is>
-          <t>1 (+ repuestos)</t>
+          <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
         </is>
       </c>
       <c r="J27" s="86" t="inlineStr">
         <is>
-          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
+          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
         </is>
       </c>
       <c r="K27" s="87" t="n"/>
       <c r="L27" s="87" t="n"/>
       <c r="M27" s="86" t="inlineStr">
         <is>
-          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
+          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
         </is>
       </c>
       <c r="N27" s="87" t="n"/>
       <c r="O27" s="87" t="n"/>
     </row>
-    <row r="28" ht="684" customHeight="1">
+    <row r="28" ht="600" customHeight="1">
       <c r="A28" s="86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" s="86" t="inlineStr">
         <is>
-          <t>Filtro final (etapa 2)</t>
+          <t>Estructura de unión y soportes</t>
         </is>
       </c>
       <c r="C28" s="87" t="n"/>
       <c r="D28" s="86" t="inlineStr">
         <is>
-          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
+          <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
         </is>
       </c>
       <c r="E28" s="87" t="n"/>
       <c r="F28" s="87" t="n"/>
       <c r="G28" s="86" t="inlineStr">
         <is>
-          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
+          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
         </is>
       </c>
       <c r="H28" s="87" t="n"/>
       <c r="I28" s="86" t="inlineStr">
         <is>
-          <t>1 (+ repuestos)</t>
+          <t>1 + Lote</t>
         </is>
       </c>
       <c r="J28" s="86" t="inlineStr">
         <is>
-          <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
+          <t>Fabricación local a partir de planos del submittal del ventilador</t>
         </is>
       </c>
       <c r="K28" s="87" t="n"/>
       <c r="L28" s="87" t="n"/>
       <c r="M28" s="86" t="inlineStr">
         <is>
-          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
+          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
         </is>
       </c>
       <c r="N28" s="87" t="n"/>
       <c r="O28" s="87" t="n"/>
     </row>
-    <row r="29" ht="418" customHeight="1">
+    <row r="29" ht="700" customHeight="1">
       <c r="A29" s="86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" s="86" t="inlineStr">
         <is>
-          <t>Marcos portafiltros</t>
+          <t>Cubierta intemperie</t>
         </is>
       </c>
       <c r="C29" s="87" t="n"/>
       <c r="D29" s="86" t="inlineStr">
         <is>
-          <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
+          <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
         </is>
       </c>
       <c r="E29" s="87" t="n"/>
       <c r="F29" s="87" t="n"/>
       <c r="G29" s="86" t="inlineStr">
         <is>
-          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
+          <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
         </is>
       </c>
       <c r="H29" s="87" t="n"/>
       <c r="I29" s="86" t="inlineStr">
         <is>
-          <t>1 juego</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" s="86" t="inlineStr">
         <is>
-          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
+          <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
         </is>
       </c>
       <c r="K29" s="87" t="n"/>
       <c r="L29" s="87" t="n"/>
       <c r="M29" s="86" t="inlineStr">
         <is>
-          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
       <c r="N29" s="87" t="n"/>
       <c r="O29" s="87" t="n"/>
     </row>
-    <row r="30" ht="456" customHeight="1">
+    <row r="30" ht="350" customHeight="1">
       <c r="A30" s="86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" s="86" t="inlineStr">
         <is>
-          <t>Rejillas de descarga</t>
+          <t>Malla de protección interior</t>
         </is>
       </c>
       <c r="C30" s="87" t="n"/>
       <c r="D30" s="86" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
+          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
         </is>
       </c>
       <c r="E30" s="87" t="n"/>
       <c r="F30" s="87" t="n"/>
       <c r="G30" s="86" t="inlineStr">
         <is>
-          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
+          <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
         </is>
       </c>
       <c r="H30" s="87" t="n"/>
       <c r="I30" s="86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" s="86" t="inlineStr">
         <is>
-          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
+          <t>Fabricación local según submittal</t>
         </is>
       </c>
       <c r="K30" s="87" t="n"/>
       <c r="L30" s="87" t="n"/>
       <c r="M30" s="86" t="inlineStr">
         <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
       <c r="N30" s="87" t="n"/>
       <c r="O30" s="87" t="n"/>
     </row>
-    <row r="31" ht="380" customHeight="1">
+    <row r="31" ht="800" customHeight="1">
       <c r="A31" s="86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" s="86" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
+          <t>Selladores</t>
         </is>
       </c>
       <c r="C31" s="87" t="n"/>
       <c r="D31" s="86" t="inlineStr">
         <is>
-          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
+          <t>Sellado de pasamuros, marcos y empalmes</t>
         </is>
       </c>
       <c r="E31" s="87" t="n"/>
       <c r="F31" s="87" t="n"/>
       <c r="G31" s="86" t="inlineStr">
         <is>
-          <t>Inox 316</t>
+          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
         </is>
       </c>
       <c r="H31" s="87" t="n"/>
       <c r="I31" s="86" t="inlineStr">
         <is>
-          <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="J31" s="86" t="inlineStr">
         <is>
-          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
+          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
         </is>
       </c>
       <c r="K31" s="87" t="n"/>
       <c r="L31" s="87" t="n"/>
       <c r="M31" s="86" t="inlineStr">
         <is>
-          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
+          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
         </is>
       </c>
       <c r="N31" s="87" t="n"/>
       <c r="O31" s="87" t="n"/>
     </row>
-    <row r="32" ht="456" customHeight="1">
+    <row r="32" ht="350" customHeight="1">
       <c r="A32" s="86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B32" s="86" t="inlineStr">
         <is>
-          <t>Estructura de unión y soportes</t>
+          <t>Protecciones eléctricas y tablero</t>
         </is>
       </c>
       <c r="C32" s="87" t="n"/>
       <c r="D32" s="86" t="inlineStr">
         <is>
-          <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
+          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
         </is>
       </c>
       <c r="E32" s="87" t="n"/>
       <c r="F32" s="87" t="n"/>
       <c r="G32" s="86" t="inlineStr">
         <is>
-          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
         </is>
       </c>
       <c r="H32" s="87" t="n"/>
       <c r="I32" s="86" t="inlineStr">
         <is>
-          <t>1 + Lote</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" s="86" t="inlineStr">
         <is>
-          <t>Fabricación local a partir de planos del submittal del ventilador</t>
+          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
         </is>
       </c>
       <c r="K32" s="87" t="n"/>
       <c r="L32" s="87" t="n"/>
       <c r="M32" s="86" t="inlineStr">
         <is>
-          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
         </is>
       </c>
       <c r="N32" s="87" t="n"/>
       <c r="O32" s="87" t="n"/>
     </row>
-    <row r="33" ht="532" customHeight="1">
+    <row r="33" ht="300" customHeight="1">
       <c r="A33" s="86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B33" s="86" t="inlineStr">
         <is>
-          <t>Cubierta intemperie</t>
+          <t>Cableado y canalización</t>
         </is>
       </c>
       <c r="C33" s="87" t="n"/>
       <c r="D33" s="86" t="inlineStr">
         <is>
-          <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
+          <t>Circuito de alimentación del motor 0.75 HP</t>
         </is>
       </c>
       <c r="E33" s="87" t="n"/>
       <c r="F33" s="87" t="n"/>
       <c r="G33" s="86" t="inlineStr">
         <is>
-          <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
+          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
         </is>
       </c>
       <c r="H33" s="87" t="n"/>
       <c r="I33" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="J33" s="86" t="inlineStr">
         <is>
-          <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
+          <t>Suministro nacional certificado RETIE</t>
         </is>
       </c>
       <c r="K33" s="87" t="n"/>
       <c r="L33" s="87" t="n"/>
       <c r="M33" s="86" t="inlineStr">
         <is>
-          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
+          <t>Requisito RETIE / NTC 2050</t>
         </is>
       </c>
       <c r="N33" s="87" t="n"/>
       <c r="O33" s="87" t="n"/>
     </row>
-    <row r="34" ht="266" customHeight="1">
-      <c r="A34" s="86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B34" s="86" t="inlineStr">
-        <is>
-          <t>Malla de protección interior</t>
-        </is>
-      </c>
-      <c r="C34" s="87" t="n"/>
-      <c r="D34" s="86" t="inlineStr">
-        <is>
-          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
-        </is>
-      </c>
-      <c r="E34" s="87" t="n"/>
-      <c r="F34" s="87" t="n"/>
-      <c r="G34" s="86" t="inlineStr">
-        <is>
-          <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
-        </is>
-      </c>
-      <c r="H34" s="87" t="n"/>
-      <c r="I34" s="86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" s="86" t="inlineStr">
-        <is>
-          <t>Fabricación local según submittal</t>
-        </is>
-      </c>
-      <c r="K34" s="87" t="n"/>
-      <c r="L34" s="87" t="n"/>
-      <c r="M34" s="86" t="inlineStr">
-        <is>
-          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
-        </is>
-      </c>
-      <c r="N34" s="87" t="n"/>
-      <c r="O34" s="87" t="n"/>
-    </row>
-    <row r="35" ht="608" customHeight="1">
-      <c r="A35" s="86" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B35" s="86" t="inlineStr">
-        <is>
-          <t>Selladores</t>
-        </is>
-      </c>
-      <c r="C35" s="87" t="n"/>
-      <c r="D35" s="86" t="inlineStr">
-        <is>
-          <t>Sellado de pasamuros, marcos y empalmes</t>
-        </is>
-      </c>
-      <c r="E35" s="87" t="n"/>
-      <c r="F35" s="87" t="n"/>
-      <c r="G35" s="86" t="inlineStr">
-        <is>
-          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
-        </is>
-      </c>
-      <c r="H35" s="87" t="n"/>
-      <c r="I35" s="86" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
-      <c r="J35" s="86" t="inlineStr">
-        <is>
-          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
-        </is>
-      </c>
-      <c r="K35" s="87" t="n"/>
-      <c r="L35" s="87" t="n"/>
-      <c r="M35" s="86" t="inlineStr">
-        <is>
-          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
-        </is>
-      </c>
-      <c r="N35" s="87" t="n"/>
-      <c r="O35" s="87" t="n"/>
-    </row>
-    <row r="36" ht="266" customHeight="1">
-      <c r="A36" s="86" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B36" s="86" t="inlineStr">
-        <is>
-          <t>Protecciones eléctricas y tablero</t>
-        </is>
-      </c>
-      <c r="C36" s="87" t="n"/>
-      <c r="D36" s="86" t="inlineStr">
-        <is>
-          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
-        </is>
-      </c>
-      <c r="E36" s="87" t="n"/>
-      <c r="F36" s="87" t="n"/>
-      <c r="G36" s="86" t="inlineStr">
-        <is>
-          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
-        </is>
-      </c>
-      <c r="H36" s="87" t="n"/>
-      <c r="I36" s="86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" s="86" t="inlineStr">
-        <is>
-          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
-        </is>
-      </c>
-      <c r="K36" s="87" t="n"/>
-      <c r="L36" s="87" t="n"/>
-      <c r="M36" s="86" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
-        </is>
-      </c>
-      <c r="N36" s="87" t="n"/>
-      <c r="O36" s="87" t="n"/>
-    </row>
-    <row r="37" ht="228" customHeight="1">
-      <c r="A37" s="86" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B37" s="86" t="inlineStr">
-        <is>
-          <t>Cableado y canalización</t>
-        </is>
-      </c>
-      <c r="C37" s="87" t="n"/>
-      <c r="D37" s="86" t="inlineStr">
-        <is>
-          <t>Circuito de alimentación del motor 0.75 HP</t>
-        </is>
-      </c>
-      <c r="E37" s="87" t="n"/>
-      <c r="F37" s="87" t="n"/>
-      <c r="G37" s="86" t="inlineStr">
-        <is>
-          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
-        </is>
-      </c>
-      <c r="H37" s="87" t="n"/>
-      <c r="I37" s="86" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
-      <c r="J37" s="86" t="inlineStr">
-        <is>
-          <t>Suministro nacional certificado RETIE</t>
-        </is>
-      </c>
-      <c r="K37" s="87" t="n"/>
-      <c r="L37" s="87" t="n"/>
-      <c r="M37" s="86" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050</t>
-        </is>
-      </c>
-      <c r="N37" s="87" t="n"/>
-      <c r="O37" s="87" t="n"/>
-    </row>
-    <row r="38" ht="38" customHeight="1"/>
-    <row r="39" ht="76" customHeight="1">
-      <c r="A39" s="82" t="inlineStr">
+    <row r="34" ht="50" customHeight="1"/>
+    <row r="35" ht="100" customHeight="1">
+      <c r="A35" s="82" t="inlineStr">
         <is>
           <t>3. Notas de suministro</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="570" customHeight="1">
-      <c r="A40" s="83" t="inlineStr">
+    <row r="36" ht="550" customHeight="1">
+      <c r="A36" s="83" t="inlineStr">
         <is>
           <t>3.1. Los ítems 1, 4, 8 y 9 requieren cotización formal con submittal: la selección final de RPM del ventilador mural Ø560 mm (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar; las dimensiones de la estructura de unión (ítem 8) y de la cubierta intemperie (ítem 9) se definen con los planos del submittal del ventilador.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="38" customHeight="1"/>
-    <row r="42" ht="532" customHeight="1">
-      <c r="A42" s="83" t="inlineStr">
+    <row r="37" ht="500" customHeight="1">
+      <c r="A37" s="83" t="inlineStr">
         <is>
           <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="38" customHeight="1"/>
-    <row r="44" ht="418" customHeight="1">
-      <c r="A44" s="83" t="inlineStr">
+    <row r="38" ht="400" customHeight="1">
+      <c r="A38" s="83" t="inlineStr">
         <is>
           <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="86">
+    <mergeCell ref="G21:H21"/>
     <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="G23:H23"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="M21:O21"/>
     <mergeCell ref="J25:L25"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="M24:O24"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="G34:H34"/>
     <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D23:F23"/>
     <mergeCell ref="J29:L29"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="M20:O20"/>
     <mergeCell ref="B1:B5"/>
     <mergeCell ref="J24:L24"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A19:O20"/>
+    <mergeCell ref="M22:O22"/>
     <mergeCell ref="M31:O31"/>
     <mergeCell ref="J26:L26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M37:O37"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="M26:O26"/>
-    <mergeCell ref="A22:O22"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M23:O23"/>
     <mergeCell ref="J33:L33"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="J28:L28"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="A14:O15"/>
-    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D21:F21"/>
     <mergeCell ref="J30:L30"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="D32:F32"/>
@@ -4779,40 +4752,34 @@
     <mergeCell ref="M30:O30"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="M33:O33"/>
-    <mergeCell ref="A40:O41"/>
-    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="D33:F33"/>
+    <mergeCell ref="A35:O35"/>
     <mergeCell ref="M32:O32"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:A5"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="A39:O39"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="A42:O43"/>
-    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D22:F22"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A44:O45"/>
-    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J20:L20"/>
     <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="J22:L22"/>
     <mergeCell ref="J31:L31"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="J21:L21"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J23:L23"/>
     <mergeCell ref="D26:F26"/>
-    <mergeCell ref="M34:O34"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="G31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
